--- a/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UC EMPRENDEDORA E INNOVADORA)(1-63).xlsx
+++ b/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UC EMPRENDEDORA E INNOVADORA)(1-63).xlsx
@@ -124,10 +124,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -176,10 +176,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -496,7 +496,7 @@
         <v>46252.40677083333</v>
       </c>
       <c r="D2" t="str">
-        <v>clorenarodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -525,7 +525,7 @@
         <v>46252.40859953704</v>
       </c>
       <c r="D3" t="str">
-        <v>andresgonzalez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -557,7 +557,7 @@
         <v>46252.41857638889</v>
       </c>
       <c r="D4" t="str">
-        <v>vnancy@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -589,7 +589,7 @@
         <v>46252.42644675926</v>
       </c>
       <c r="D5" t="str">
-        <v>ncrubio@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -618,7 +618,7 @@
         <v>46252.43137731482</v>
       </c>
       <c r="D6" t="str">
-        <v>hcastrof@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -650,7 +650,7 @@
         <v>46252.43171296296</v>
       </c>
       <c r="D7" t="str">
-        <v>nestorjgarcia@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -682,7 +682,7 @@
         <v>46252.43858796296</v>
       </c>
       <c r="D8" t="str">
-        <v>sfvergara@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>46252.43866898148</v>
       </c>
       <c r="D9" t="str">
-        <v>smurciac@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -740,7 +740,7 @@
         <v>46252.43892361111</v>
       </c>
       <c r="D10" t="str">
-        <v>dfpachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -769,7 +769,7 @@
         <v>46252.43902777778</v>
       </c>
       <c r="D11" t="str">
-        <v>cbosa@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -801,7 +801,7 @@
         <v>46252.644583333335</v>
       </c>
       <c r="D12" t="str">
-        <v>erpena@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -830,7 +830,7 @@
         <v>46252.644953703704</v>
       </c>
       <c r="D13" t="str">
-        <v>lscortes@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -859,7 +859,7 @@
         <v>46252.64503472222</v>
       </c>
       <c r="D14" t="str">
-        <v>sjanethrincon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -888,7 +888,7 @@
         <v>46252.64604166667</v>
       </c>
       <c r="D15" t="str">
-        <v>jbriseno@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -920,7 +920,7 @@
         <v>46252.646215277775</v>
       </c>
       <c r="D16" t="str">
-        <v>jhonsbarreto@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -952,7 +952,7 @@
         <v>46252.64650462963</v>
       </c>
       <c r="D17" t="str">
-        <v>ynmolina@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -984,7 +984,7 @@
         <v>46252.646678240744</v>
       </c>
       <c r="D18" t="str">
-        <v>mehueso@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1016,7 +1016,7 @@
         <v>46252.649502314816</v>
       </c>
       <c r="D19" t="str">
-        <v>johansantiagocastillo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1045,7 +1045,7 @@
         <v>46252.6496412037</v>
       </c>
       <c r="D20" t="str">
-        <v>bsebastiancastillo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1074,7 +1074,7 @@
         <v>46252.650671296295</v>
       </c>
       <c r="D21" t="str">
-        <v>nmhuertas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1103,7 +1103,7 @@
         <v>46252.65075231482</v>
       </c>
       <c r="D22" t="str">
-        <v>jalayon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1132,7 +1132,7 @@
         <v>46252.651296296295</v>
       </c>
       <c r="D23" t="str">
-        <v>ndalarcon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>46252.65168981482</v>
       </c>
       <c r="D24" t="str">
-        <v>mfernandaurrego@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1190,7 +1190,7 @@
         <v>46252.65179398148</v>
       </c>
       <c r="D25" t="str">
-        <v>ejuranypineda@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1222,7 +1222,7 @@
         <v>46252.65493055555</v>
       </c>
       <c r="D26" t="str">
-        <v>dstephaniromero@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1251,7 +1251,7 @@
         <v>46252.65525462963</v>
       </c>
       <c r="D27" t="str">
-        <v>gtgutierrez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1283,7 +1283,7 @@
         <v>46252.65550925926</v>
       </c>
       <c r="D28" t="str">
-        <v>karendortiz@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1315,7 +1315,7 @@
         <v>46252.6562037037</v>
       </c>
       <c r="D29" t="str">
-        <v>ahvanegas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1344,7 +1344,7 @@
         <v>46252.65813657407</v>
       </c>
       <c r="D30" t="str">
-        <v>nalavardo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1376,7 +1376,7 @@
         <v>46252.65813657407</v>
       </c>
       <c r="D31" t="str">
-        <v>lvchiquiza@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1408,7 +1408,7 @@
         <v>46252.663136574076</v>
       </c>
       <c r="D32" t="str">
-        <v>jefersonalejandroramirez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1440,7 +1440,7 @@
         <v>46252.66333333333</v>
       </c>
       <c r="D33" t="str">
-        <v>rguilombo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1469,7 +1469,7 @@
         <v>46252.664988425924</v>
       </c>
       <c r="D34" t="str">
-        <v>yandreyrincon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1498,7 +1498,7 @@
         <v>46252.66569444445</v>
       </c>
       <c r="D35" t="str">
-        <v>jprocha@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1527,7 +1527,7 @@
         <v>46252.66621527778</v>
       </c>
       <c r="D36" t="str">
-        <v>kaprada@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1556,7 +1556,7 @@
         <v>46252.66627314815</v>
       </c>
       <c r="D37" t="str">
-        <v>rjdelgado@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1588,7 +1588,7 @@
         <v>46252.67201388889</v>
       </c>
       <c r="D38" t="str">
-        <v>lncajamarca@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>46252.67261574074</v>
       </c>
       <c r="D39" t="str">
-        <v>yessicatrodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1649,7 +1649,7 @@
         <v>46252.672638888886</v>
       </c>
       <c r="D40" t="str">
-        <v>angiecrojas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1681,7 +1681,7 @@
         <v>46252.672743055555</v>
       </c>
       <c r="D41" t="str">
-        <v>nleonr@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1710,7 +1710,7 @@
         <v>46252.67292824074</v>
       </c>
       <c r="D42" t="str">
-        <v>empachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1739,7 +1739,7 @@
         <v>46252.67359953704</v>
       </c>
       <c r="D43" t="str">
-        <v>hacorredor@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1768,7 +1768,7 @@
         <v>46252.67427083333</v>
       </c>
       <c r="D44" t="str">
-        <v>jcarinagomez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1797,7 +1797,7 @@
         <v>46252.68002314815</v>
       </c>
       <c r="D45" t="str">
-        <v>yzsantana@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1826,7 +1826,7 @@
         <v>46252.68042824074</v>
       </c>
       <c r="D46" t="str">
-        <v>hcarolinasierra@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1858,7 +1858,7 @@
         <v>46252.68103009259</v>
       </c>
       <c r="D47" t="str">
-        <v>vjcastro@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -1890,7 +1890,7 @@
         <v>46252.68163194445</v>
       </c>
       <c r="D48" t="str">
-        <v>decasas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -1919,7 +1919,7 @@
         <v>46252.682118055556</v>
       </c>
       <c r="D49" t="str">
-        <v>paulaaperez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -1948,7 +1948,7 @@
         <v>46252.68251157407</v>
       </c>
       <c r="D50" t="str">
-        <v>kxvillamil@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -1980,7 +1980,7 @@
         <v>46252.682592592595</v>
       </c>
       <c r="D51" t="str">
-        <v>krociomurcia@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2012,7 +2012,7 @@
         <v>46252.80914351852</v>
       </c>
       <c r="D52" t="str">
-        <v>jfnova@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2047,7 +2047,7 @@
         <v>46252.80936342593</v>
       </c>
       <c r="D53" t="str">
-        <v>tfhernandez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2082,7 +2082,7 @@
         <v>46252.81990740741</v>
       </c>
       <c r="D54" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I54" t="str">
         <v>Graduados</v>
@@ -2114,7 +2114,7 @@
         <v>46252.82048611111</v>
       </c>
       <c r="D55" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I55" t="str">
         <v>Graduados</v>
@@ -2146,7 +2146,7 @@
         <v>46252.82450231481</v>
       </c>
       <c r="D56" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I56" t="str">
         <v>Graduados</v>
@@ -2178,7 +2178,7 @@
         <v>46252.82765046296</v>
       </c>
       <c r="D57" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I57" t="str">
         <v>Graduados</v>
@@ -2207,7 +2207,7 @@
         <v>46252.828622685185</v>
       </c>
       <c r="D58" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I58" t="str">
         <v>Graduados</v>
@@ -2239,7 +2239,7 @@
         <v>46252.83011574074</v>
       </c>
       <c r="D59" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I59" t="str">
         <v>Graduados</v>
@@ -2268,7 +2268,7 @@
         <v>46252.8353587963</v>
       </c>
       <c r="D60" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I60" t="str">
         <v>Graduados</v>
@@ -2300,7 +2300,7 @@
         <v>46252.83708333333</v>
       </c>
       <c r="D61" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I61" t="str">
         <v>Graduados</v>
@@ -2332,7 +2332,7 @@
         <v>46252.84574074074</v>
       </c>
       <c r="D62" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I62" t="str">
         <v>Graduados</v>
@@ -2364,7 +2364,7 @@
         <v>46252.84591435185</v>
       </c>
       <c r="D63" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I63" t="str">
         <v>Graduados</v>
@@ -2396,7 +2396,7 @@
         <v>46252.84594907407</v>
       </c>
       <c r="D64" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I64" t="str">
         <v>Graduados</v>
